--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_FCB.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_FCB.xlsx
@@ -2371,7 +2371,11 @@
           <t>FCB_A._MARQUES</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>242941</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>A. Marques</t>
@@ -4405,7 +4409,11 @@
           <t>FCB_A._MARQUES</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>242941</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>A. Marques</t>
@@ -6227,7 +6235,11 @@
           <t>FCB_A._MARQUES</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>242941</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>A. Marques</t>
